--- a/data_excel/database.xlsx
+++ b/data_excel/database.xlsx
@@ -16,6 +16,7 @@
     <sheet name="PasswordResetTokens" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="KanbanConfig" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Leads" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Jarvis_Brain" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,6 +611,80 @@
       </c>
       <c r="F6" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WILKSON ROBERTO SELEDONI DE ARAUJO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>will.adm@idealcentro.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>b'$2b$12$aBfqQAkVDZ5jlMShIowcD.cZWcH3zWcaIJUbuRXGsISqQmPVBypm.'</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID_Conhecimento</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Palavra_Chave</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Resposta</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Usuario_Sugeriu</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data_Criacao</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -623,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,7 +1605,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46086.41127671118</v>
+        <v>46086.41127671296</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1545,7 +1620,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46086.4173905936</v>
+        <v>46086.41739059028</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1560,7 +1635,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46086.42274087486</v>
+        <v>46086.42274087963</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1575,7 +1650,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46086.42444272638</v>
+        <v>46086.42444273148</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1590,7 +1665,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46086.42469374492</v>
+        <v>46086.42469375</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1605,7 +1680,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46086.42678359763</v>
+        <v>46086.42678359953</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1615,6 +1690,321 @@
       <c r="C66" t="inlineStr">
         <is>
           <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46087.54053950231</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46087.54395648148</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46087.54910627315</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46087.55243188657</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46087.56316349537</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46087.5647837963</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46087.56804850695</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46087.59208939815</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Logout do usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46087.59220480324</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46087.59278393519</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Logout do usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46087.59314372685</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46087.56068225695</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46087.56900524306</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46087.70863608796</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AVISO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tentativa de login falhou para o email: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46087.70874046296</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46087.71052313657</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Logout do usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46087.71063716435</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46087.58827232639</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46087.5896616088</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46087.59661519676</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46087.59785261574</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: admin@email.com</t>
         </is>
       </c>
     </row>
@@ -1782,7 +2172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,6 +2221,31 @@
           <t>ID_Lead</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Antigo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mensagem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1860,6 +2275,11 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1893,6 +2313,11 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1926,6 +2351,11 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1959,6 +2389,11 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1988,6 +2423,11 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2021,6 +2461,11 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2054,6 +2499,11 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2087,6 +2537,11 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2120,6 +2575,11 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2153,6 +2613,11 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2182,6 +2647,11 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2215,6 +2685,11 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2248,6 +2723,11 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2761,11 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,6 +2799,11 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2347,6 +2837,11 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2380,6 +2875,11 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2413,6 +2913,11 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2446,6 +2951,11 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2479,6 +2989,11 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2512,6 +3027,11 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2545,6 +3065,11 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2578,6 +3103,11 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2611,6 +3141,11 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2644,6 +3179,11 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2677,6 +3217,11 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2710,6 +3255,11 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2743,6 +3293,11 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2776,6 +3331,11 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2809,6 +3369,11 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2842,6 +3407,11 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2875,6 +3445,11 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2908,6 +3483,11 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2941,6 +3521,11 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2970,6 +3555,11 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3003,6 +3593,11 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3036,6 +3631,11 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3069,6 +3669,11 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3102,6 +3707,11 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3131,6 +3741,11 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3164,6 +3779,11 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3197,6 +3817,11 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3226,6 +3851,11 @@
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3259,6 +3889,11 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3292,6 +3927,11 @@
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3327,6 +3967,11 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3360,6 +4005,11 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3393,6 +4043,11 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3426,6 +4081,1129 @@
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>66</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" s="2" t="n">
+        <v>46087.59427817129</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Criado</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Lead cadastrado no sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>67</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" s="2" t="n">
+        <v>46087.57226896991</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Avançado para Em Progresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>68</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" s="2" t="n">
+        <v>46087.57229508102</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Recuado para Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>69</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" s="2" t="n">
+        <v>46087.57232572917</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Avançado para Em Progresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>70</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" s="2" t="n">
+        <v>46087.5723497338</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Perdidos</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>❌ PROCESSO ENCERRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>71</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" s="2" t="n">
+        <v>46087.57262715277</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Comentário</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>72</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" s="2" t="n">
+        <v>46087.57666050926</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Criado</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Lead cadastrado no sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>73</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" s="2" t="n">
+        <v>46087.57680717592</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Avançado para Em Progresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>74</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" s="2" t="n">
+        <v>46087.57683575231</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Recuado para Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>75</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" s="2" t="n">
+        <v>46087.57701174769</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Avançado para Em Progresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>76</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" s="2" t="n">
+        <v>46087.57730224537</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Recuado para Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>77</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" s="2" t="n">
+        <v>46087.57819049768</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>[{"task": "Coletar informa\u00e7\u00f5es b\u00e1sicas", "done": false}, {"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>[{"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>78</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" s="2" t="n">
+        <v>46087.5782137037</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>[{"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>[{"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>79</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" s="2" t="n">
+        <v>46087.57823030093</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>[{"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>80</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" s="2" t="n">
+        <v>46087.57824601852</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>81</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" s="2" t="n">
+        <v>46087.57828748842</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>[{"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>82</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" s="2" t="n">
+        <v>46087.57831666667</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>[{"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>83</v>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" s="2" t="n">
+        <v>46087.57848636574</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Comentário</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ola</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>84</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" s="2" t="n">
+        <v>46087.57917813658</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Razao_Social</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>fjsj</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>fjsj</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>85</v>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" s="2" t="n">
+        <v>46087.57917818287</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>252525252</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>252525252</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>86</v>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" s="2" t="n">
+        <v>46087.57917822916</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>87</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" s="2" t="n">
+        <v>46087.57917827546</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Nucleo</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>88</v>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" s="2" t="n">
+        <v>46087.57917832176</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Prioridade</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>89</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" s="2" t="n">
+        <v>46087.57917836805</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Risco</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>90</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" s="2" t="n">
+        <v>46087.57917842593</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Esforco</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>91</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" s="2" t="n">
+        <v>46087.57917847222</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Prazo</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>92</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" s="2" t="n">
+        <v>46087.57917854167</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3553,7 +5331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3579,7 +5357,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3592,7 +5370,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Em Progresso</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3601,20 +5379,24 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pendentes</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Propostas</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3623,15 +5405,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Reuniões</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Negociação</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ganhos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perdidos</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3645,7 +5466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3754,6 +5575,175 @@
           <t>Data_Entrada_Etapa</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Risco</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Esforco</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Nucleo</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Perdidos</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Em dia</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46087.57234976852</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46087.59427813657</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>46087.5723497338</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}, {"task": "Coletar informa\u00e7\u00f5es b\u00e1sicas", "done": false}, {"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}, {"task": "Registrar motivo da perda", "done": false}, {"task": "Agendar follow-up futuro", "done": false}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>afsas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25252525252525</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fjsj</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Em dia</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46087.57917858796</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46087.57666042824</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>46087.5773022338</v>
+      </c>
+      <c r="V3" t="n">
+        <v>252525252</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_excel/database.xlsx
+++ b/data_excel/database.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46087.58827232639</v>
+        <v>46087.72730878472</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46087.5896616088</v>
+        <v>46087.72781210648</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+          <t>Logout do usuário: admin@email.com</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46087.59661519676</v>
+        <v>46087.73141402778</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46087.59785261574</v>
+        <v>46087.76504473379</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2004,7 +2004,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Login bem-sucedido para o usuário: admin@email.com</t>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46087.7689627662</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46087.6635092635</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5204,6 +5234,482 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>93</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="2" t="n">
+        <v>46087.76781797453</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Criado</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Lead cadastrado no sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>94</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" s="2" t="n">
+        <v>46087.7681019213</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Comentário</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>95</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" s="2" t="n">
+        <v>46087.76831898148</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Etapa_Atual</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Em Progresso</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Avançado para Em Progresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>96</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" s="2" t="n">
+        <v>46087.76837149305</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Razao_Social</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>fjsj</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>fjsj</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>97</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" s="2" t="n">
+        <v>46087.76837151621</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>252525252</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>252525252</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>98</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" s="2" t="n">
+        <v>46087.76837152777</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>99</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" s="2" t="n">
+        <v>46087.76837155093</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Nucleo</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>100</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" s="2" t="n">
+        <v>46087.7683715625</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Prioridade</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>101</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" s="2" t="n">
+        <v>46087.76837157407</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Risco</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>102</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" s="2" t="n">
+        <v>46087.76837159722</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Esforco</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>103</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" s="2" t="n">
+        <v>46087.7683716088</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Prazo</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>104</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" s="2" t="n">
+        <v>46087.76837163194</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5466,7 +5972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5697,7 +6203,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Em Progresso</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -5712,14 +6218,14 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>46087.57917858796</v>
+        <v>46087.76837164352</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>46087.57666042824</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" s="2" t="n">
-        <v>46087.5773022338</v>
+        <v>46087.76831898148</v>
       </c>
       <c r="V3" t="n">
         <v>252525252</v>
@@ -5741,7 +6247,75 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"task": "Agendar primeira chamada", "done": false}, {"task": "Enviar apresenta\u00e7\u00e3o da empresa", "done": false}, {"task": "Mapear dores do cliente", "done": false}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>77777777777777</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Teate</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Em dia</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46087.76781793981</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46087.76781793981</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>46087.76781793981</v>
+      </c>
+      <c r="V4" t="n">
+        <v>222222222</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[{"task": "Coletar informa\u00e7\u00f5es b\u00e1sicas", "done": false}, {"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
         </is>
       </c>
     </row>

--- a/data_excel/database.xlsx
+++ b/data_excel/database.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46087.6635092635</v>
+        <v>46087.89762182871</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2033,6 +2033,21 @@
         </is>
       </c>
       <c r="C89" t="inlineStr">
+        <is>
+          <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46090.55168615433</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Login bem-sucedido para o usuário: rhaique.adm@idealcentro.com</t>
         </is>
@@ -2202,7 +2217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5710,6 +5725,136 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>105</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" s="2" t="n">
+        <v>46087.90528883102</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>4</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>[{"task": "Coletar informa\u00e7\u00f5es b\u00e1sicas", "done": false}, {"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>[{"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>106</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" s="2" t="n">
+        <v>46087.90534706019</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>4</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>[{"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>[{"task": "Validar telefone e email", "done": true}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>107</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" s="2" t="n">
+        <v>46090.55212581837</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Anexo</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>20260309 - Anexo Operacional.png</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Arquivo '20260309 - Anexo Operacional.png' anexado.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5722,7 +5867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5771,6 +5916,39 @@
           <t>Observacao</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20260309 - Anexo Operacional.png</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MvuRqM0-lbSegsaBQoIvOeH_KLsXjj3l/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Rhaique</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46090.55212575565</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6294,7 +6472,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>46087.76781793981</v>
+        <v>46087.90534708333</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46087.76781793981</v>
@@ -6315,7 +6493,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{"task": "Coletar informa\u00e7\u00f5es b\u00e1sicas", "done": false}, {"task": "Validar telefone e email", "done": false}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
+          <t>[{"task": "Validar telefone e email", "done": true}, {"task": "Identificar tomador de decis\u00e3o", "done": false}]</t>
         </is>
       </c>
     </row>
